--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484580_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484580_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.720499999999999</v>
+        <v>9.413</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2655</v>
+        <v>3.0076</v>
       </c>
       <c r="F2" t="n">
-        <v>6.455</v>
+        <v>6.4055</v>
       </c>
       <c r="G2" t="n">
         <v>4.9829</v>
@@ -610,13 +610,13 @@
         <v>3.6651</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.205</v>
+        <v>-0.5124</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.9819</v>
+        <v>-1.2398</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7769</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>1.2774</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0419</v>
+        <v>7.3447</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2474</v>
+        <v>1.3025</v>
       </c>
       <c r="F3" t="n">
-        <v>5.7945</v>
+        <v>6.0422</v>
       </c>
       <c r="G3" t="n">
         <v>4.1382</v>
@@ -688,13 +688,13 @@
         <v>2.0158</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5867</v>
+        <v>0.8895</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2398</v>
+        <v>-0.1847</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8265</v>
+        <v>1.0743</v>
       </c>
       <c r="V3" t="n">
         <v>0.3011</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9606</v>
+        <v>3.5482</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8811</v>
+        <v>1.5926</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0795</v>
+        <v>1.9556</v>
       </c>
       <c r="G4" t="n">
         <v>2.4224</v>
@@ -766,13 +766,13 @@
         <v>1.0995</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.3482</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0905</v>
+        <v>-0.198</v>
       </c>
       <c r="U4" t="n">
-        <v>0.67</v>
+        <v>0.5462</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3219</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>P. ARISTA CALLAU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9709</v>
+        <v>3.5152</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1756</v>
+        <v>0.68</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1465</v>
+        <v>2.8353</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7438</v>
+        <v>2.7223</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9266</v>
+        <v>3.2383</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1828</v>
+        <v>-0.516</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5078</v>
+        <v>2.6541</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8889</v>
+        <v>2.3684</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3811</v>
+        <v>0.2857</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2361</v>
+        <v>0.0682</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0377</v>
+        <v>0.8698</v>
       </c>
       <c r="O5" t="n">
         <v>-0.8017</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1833</v>
+        <v>1.0995</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5656</v>
+        <v>2.9321</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9116</v>
+        <v>-0.3066</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.5784</v>
+        <v>-0.7854</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.4789</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0.6439</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3219</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PEÑA</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8256</v>
+        <v>3.1272</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8256</v>
+        <v>0.278</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2.8492</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8256</v>
+        <v>3.7438</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3251</v>
+        <v>4.9266</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5005</v>
+        <v>-1.1828</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8256</v>
+        <v>3.5078</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3251</v>
+        <v>3.8889</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5005</v>
+        <v>-0.3811</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.2361</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.0377</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.8017</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.5656</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.7553</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-1.1248</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.3695</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ARISTA CALLAU</t>
+          <t>D. ARIJA DE LA PEÑA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6711</v>
+        <v>2.8256</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0341</v>
+        <v>2.8256</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6371</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7223</v>
+        <v>2.8256</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2383</v>
+        <v>0.3251</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.516</v>
+        <v>2.5005</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6541</v>
+        <v>2.8256</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3684</v>
+        <v>0.3251</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2857</v>
+        <v>2.5005</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0682</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8698</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8017</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9321</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1507</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.4313</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2807</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. CAMAHORT TORRES</t>
+          <t>R. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8687</v>
+        <v>0.6654</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9189000000000001</v>
+        <v>-1.289</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0502</v>
+        <v>1.9544</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5717</v>
+        <v>1.8279</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3923</v>
+        <v>2.0554</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1794</v>
+        <v>-0.2275</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7553</v>
+        <v>1.662</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.9596</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0833</v>
+        <v>0.7024</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8164</v>
+        <v>0.1659</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7204</v>
+        <v>1.0958</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0961</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0.733</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R8" t="n">
-        <v>0.733</v>
+        <v>2.1991</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1691</v>
+        <v>-1.2462</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1637</v>
+        <v>-0.8356</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3327</v>
+        <v>-0.4107</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.267</v>
+        <v>0.6335</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. HOLGADO CUELLAR</t>
+          <t>C. CAMAHORT TORRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0279</v>
+        <v>0.5336</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5363</v>
+        <v>0.5343</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5084</v>
+        <v>-0.0007</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8279</v>
+        <v>1.5717</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0554</v>
+        <v>1.3923</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2275</v>
+        <v>0.1794</v>
       </c>
       <c r="J9" t="n">
-        <v>1.662</v>
+        <v>0.7553</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9596</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7024</v>
+        <v>0.0833</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1659</v>
+        <v>0.8164</v>
       </c>
       <c r="N9" t="n">
-        <v>1.0958</v>
+        <v>0.7204</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9298999999999999</v>
+        <v>0.0961</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1991</v>
+        <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9395</v>
+        <v>-0.5041</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0829</v>
+        <v>-0.221</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8566</v>
+        <v>-0.2832</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6335</v>
+        <v>-1.267</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="10">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3774</v>
+        <v>-1.2758</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5819</v>
+        <v>-1.4307</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2044</v>
+        <v>0.1549</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2238</v>
@@ -1312,13 +1312,13 @@
         <v>0.5498</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3814</v>
+        <v>-0.2798</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3673</v>
+        <v>-0.2161</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0142</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3219</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8466</v>
+        <v>-3.8907</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.4716</v>
+        <v>-6.268</v>
       </c>
       <c r="F12" t="n">
-        <v>2.625</v>
+        <v>2.3773</v>
       </c>
       <c r="G12" t="n">
         <v>0.3101</v>
@@ -1390,13 +1390,13 @@
         <v>2.3823</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8695</v>
+        <v>0.8254</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9872</v>
+        <v>0.1908</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8823</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-1.9109</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6355</v>
+        <v>-4.8089</v>
       </c>
       <c r="E13" t="n">
         <v>-2.5105</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1249</v>
+        <v>-2.2983</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9965</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1337</v>
+        <v>-0.3071</v>
       </c>
       <c r="T13" t="n">
         <v>-0.3122</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1785</v>
+        <v>0.0051</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5889</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>19.8919</v>
+        <v>20.7175</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.270999999999999</v>
+        <v>-1.445299999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>22.1629</v>
+        <v>22.163</v>
       </c>
       <c r="G14" t="n">
         <v>22.0182</v>
@@ -1528,7 +1528,7 @@
         <v>2.567</v>
       </c>
       <c r="M14" t="n">
-        <v>7.147799999999999</v>
+        <v>7.1478</v>
       </c>
       <c r="N14" t="n">
         <v>7.951</v>
@@ -1546,13 +1546,13 @@
         <v>18.3256</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.5641</v>
+        <v>-1.7383</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.972600000000001</v>
+        <v>-5.146999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>3.4085</v>
+        <v>3.4086</v>
       </c>
       <c r="V14" t="n">
         <v>-4.1437</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2039</v>
+        <v>5.3738</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0089</v>
+        <v>5.7782</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8051</v>
+        <v>-0.4044</v>
       </c>
       <c r="G15" t="n">
         <v>3.6535</v>
@@ -1624,13 +1624,13 @@
         <v>1.2828</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7716</v>
+        <v>0.3984</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7157</v>
+        <v>0.0536</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0559</v>
+        <v>0.3448</v>
       </c>
       <c r="V15" t="n">
         <v>0.9554</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1652</v>
+        <v>3.7878</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6081</v>
+        <v>1.1273</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5571</v>
+        <v>2.6605</v>
       </c>
       <c r="G16" t="n">
         <v>1.4983</v>
@@ -1702,13 +1702,13 @@
         <v>1.6493</v>
       </c>
       <c r="S16" t="n">
-        <v>1.028</v>
+        <v>0.6506</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3462</v>
+        <v>-0.1346</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6818</v>
+        <v>0.7852</v>
       </c>
       <c r="V16" t="n">
         <v>-0.0104</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.379</v>
+        <v>0.6222</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1289</v>
+        <v>-0.8405</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5079</v>
+        <v>1.4627</v>
       </c>
       <c r="G18" t="n">
         <v>-0.663</v>
@@ -1858,13 +1858,13 @@
         <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8746</v>
+        <v>1.1178</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6071</v>
+        <v>-0.3186</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4816</v>
+        <v>1.4364</v>
       </c>
       <c r="V18" t="n">
         <v>1.267</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1006</v>
+        <v>0.1501</v>
       </c>
       <c r="E19" t="n">
         <v>-0.08840000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.189</v>
+        <v>0.2385</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1157</v>
@@ -1936,13 +1936,13 @@
         <v>0.3665</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1502</v>
+        <v>-0.1007</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0401</v>
+        <v>0.0094</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7214</v>
+        <v>-0.5757</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.065</v>
+        <v>-1.9688</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3436</v>
+        <v>1.3931</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8199</v>
@@ -2014,13 +2014,13 @@
         <v>0.733</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0401</v>
+        <v>0.1056</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2753</v>
+        <v>-0.1791</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2351</v>
+        <v>0.2847</v>
       </c>
       <c r="V20" t="n">
         <v>0.3219</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0797</v>
+        <v>-2.4118</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3955</v>
+        <v>-1.8763</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6842</v>
+        <v>-0.5355</v>
       </c>
       <c r="G21" t="n">
         <v>-6.0045</v>
@@ -2092,13 +2092,13 @@
         <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5192</v>
+        <v>0.187</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3643</v>
+        <v>-0.1165</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1549</v>
+        <v>0.3035</v>
       </c>
       <c r="V21" t="n">
         <v>2.8559</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ALVAREZ LENCINA</t>
+          <t>D. MICHAEL KING</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3444</v>
+        <v>-3.0474</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9551</v>
+        <v>-4.4348</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3893</v>
+        <v>1.3873</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.5583</v>
+        <v>-2.1291</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4202</v>
+        <v>-2.7956</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1381</v>
+        <v>0.6665</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4791</v>
+        <v>-0.7703</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2387</v>
+        <v>-1.437</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2404</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0792</v>
+        <v>-1.3588</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1815</v>
+        <v>-1.3585</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8977000000000001</v>
+        <v>-0.0003</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1833</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0995</v>
+        <v>1.4661</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7087</v>
+        <v>0.0138</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2036</v>
+        <v>-0.6433</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9123</v>
+        <v>0.657</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="W22" t="n">
         <v>0.6439</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3219</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. MICHAEL KING</t>
+          <t>A. ALVAREZ LENCINA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4364</v>
+        <v>-3.7101</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8194</v>
+        <v>-3.1474</v>
       </c>
       <c r="F23" t="n">
-        <v>1.383</v>
+        <v>-0.5627</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1291</v>
+        <v>-4.5583</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.7956</v>
+        <v>-2.4202</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6665</v>
+        <v>-2.1381</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7703</v>
+        <v>-2.4791</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.437</v>
+        <v>-1.2387</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6667999999999999</v>
+        <v>-1.2404</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3588</v>
+        <v>-2.0792</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3585</v>
+        <v>-1.1815</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0003</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.1991</v>
+        <v>0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3752</v>
+        <v>0.343</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0279</v>
+        <v>-0.3959</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.7389</v>
       </c>
       <c r="V23" t="n">
-        <v>1.267</v>
+        <v>0.3219</v>
       </c>
       <c r="W23" t="n">
         <v>0.6439</v>
       </c>
       <c r="X23" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1616</v>
+        <v>-6.4967</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.8197</v>
+        <v>-5.2043</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3419</v>
+        <v>-1.2923</v>
       </c>
       <c r="G24" t="n">
         <v>-6.3665</v>
@@ -2326,13 +2326,13 @@
         <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9667</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4374</v>
+        <v>0.0528</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5292</v>
+        <v>0.5788</v>
       </c>
       <c r="V24" t="n">
         <v>-0.945</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.8983</v>
+        <v>-6.9289</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.6018</v>
+        <v>-5.4095</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2965</v>
+        <v>-1.5195</v>
       </c>
       <c r="G25" t="n">
         <v>-6.6561</v>
@@ -2404,13 +2404,13 @@
         <v>1.2828</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.258</v>
+        <v>-0.2886</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0829</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8249</v>
+        <v>0.602</v>
       </c>
       <c r="V25" t="n">
         <v>-1.267</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.3739</v>
+        <v>-7.2894</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.1814</v>
+        <v>-7.3737</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1925</v>
+        <v>0.0843</v>
       </c>
       <c r="G26" t="n">
         <v>-1.132</v>
@@ -2482,13 +2482,13 @@
         <v>1.6493</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0621</v>
+        <v>0.1467</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5339</v>
+        <v>-0.7262</v>
       </c>
       <c r="U26" t="n">
-        <v>0.596</v>
+        <v>0.8729</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6231</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-19.8917</v>
+        <v>-19.2508</v>
       </c>
       <c r="E27" t="n">
         <v>-22.1629</v>
       </c>
       <c r="F27" t="n">
-        <v>2.271100000000001</v>
+        <v>2.912</v>
       </c>
       <c r="G27" t="n">
         <v>-22.018</v>
@@ -2539,7 +2539,7 @@
         <v>-7.950899999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8031999999999999</v>
+        <v>0.803199999999999</v>
       </c>
       <c r="M27" t="n">
         <v>-14.8703</v>
@@ -2560,13 +2560,13 @@
         <v>13.7442</v>
       </c>
       <c r="S27" t="n">
-        <v>2.5642</v>
+        <v>3.2052</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.4086</v>
+        <v>-3.4085</v>
       </c>
       <c r="U27" t="n">
-        <v>5.9725</v>
+        <v>6.6136</v>
       </c>
       <c r="V27" t="n">
         <v>4.1436</v>
